--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,21 @@
   </si>
   <si>
     <t xml:space="preserve">planning my sechduled </t>
+  </si>
+  <si>
+    <t>busy day with classes felt tier afterward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weekend laundry cleaning cooking </t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>relexed weekend with household work</t>
+  </si>
+  <si>
+    <t>I was totally drained today after coming back</t>
   </si>
 </sst>
 </file>
@@ -847,8 +862,10 @@
   <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="6" width="11" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -986,7 +1003,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F6" s="9">
         <v>250</v>
@@ -995,15 +1012,15 @@
         <v>5</v>
       </c>
       <c r="H6" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>56</v>
@@ -1032,7 +1049,7 @@
         <v>50</v>
       </c>
       <c r="E7" s="9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7" s="9">
         <v>350</v>
@@ -1041,15 +1058,15 @@
         <v>7</v>
       </c>
       <c r="H7" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I7" s="10">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>49</v>
@@ -1081,21 +1098,21 @@
         <v>0</v>
       </c>
       <c r="F8" s="9">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G8" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="9">
         <v>480</v>
       </c>
       <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>940</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>57</v>
@@ -1110,93 +1127,189 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+    <row r="9" spans="1:14" ht="30">
+      <c r="A9" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B9" s="9">
+        <v>450</v>
+      </c>
+      <c r="C9" s="9">
+        <v>40</v>
+      </c>
+      <c r="D9" s="9">
+        <v>30</v>
+      </c>
+      <c r="E9" s="9">
+        <v>30</v>
+      </c>
+      <c r="F9" s="9">
+        <v>250</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5</v>
+      </c>
+      <c r="H9" s="9">
+        <v>180</v>
+      </c>
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+        <v>460</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="30">
+      <c r="A10" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B10" s="9">
+        <v>510</v>
+      </c>
+      <c r="C10" s="9">
+        <v>20</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>500</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+        <v>410</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="30">
+      <c r="A11" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="9">
+        <v>540</v>
+      </c>
+      <c r="C11" s="9">
+        <v>60</v>
+      </c>
+      <c r="D11" s="9">
+        <v>40</v>
+      </c>
+      <c r="E11" s="9">
+        <v>40</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>180</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>860</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+        <v>580</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="30">
+      <c r="A12" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="9">
+        <v>570</v>
+      </c>
+      <c r="C12" s="9">
+        <v>60</v>
+      </c>
+      <c r="D12" s="9">
+        <v>20</v>
+      </c>
+      <c r="E12" s="9">
+        <v>35</v>
+      </c>
+      <c r="F12" s="9">
+        <v>250</v>
+      </c>
+      <c r="G12" s="9">
+        <v>5</v>
+      </c>
+      <c r="H12" s="9">
+        <v>90</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
+        <v>415</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>I was totally drained today after coming back</t>
+  </si>
+  <si>
+    <t>regular collage day with 3 classes</t>
   </si>
 </sst>
 </file>
@@ -1311,27 +1314,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+    <row r="13" spans="1:14" ht="30">
+      <c r="A13" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="9">
+        <v>360</v>
+      </c>
+      <c r="C13" s="9">
+        <v>60</v>
+      </c>
+      <c r="D13" s="9">
+        <v>20</v>
+      </c>
+      <c r="E13" s="9">
+        <v>60</v>
+      </c>
+      <c r="F13" s="9">
+        <v>150</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3</v>
+      </c>
+      <c r="H13" s="9">
+        <v>150</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>800</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+        <v>640</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,24 @@
   </si>
   <si>
     <t>regular collage day with 3 classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">busy day with 8 classes </t>
+  </si>
+  <si>
+    <t>regular college day</t>
+  </si>
+  <si>
+    <t>travelled to panipat and reached home</t>
+  </si>
+  <si>
+    <t>relexed  at home with family</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Sunday spent at home with family</t>
   </si>
 </sst>
 </file>
@@ -1361,114 +1379,234 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="A14" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="9">
+        <v>420</v>
+      </c>
+      <c r="C14" s="9">
+        <v>40</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>30</v>
+      </c>
+      <c r="F14" s="9">
+        <v>400</v>
+      </c>
+      <c r="G14" s="9">
+        <v>8</v>
+      </c>
+      <c r="H14" s="9">
+        <v>150</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="A15" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="9">
+        <v>450</v>
+      </c>
+      <c r="C15" s="9">
+        <v>60</v>
+      </c>
+      <c r="D15" s="9">
+        <v>30</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>250</v>
+      </c>
+      <c r="G15" s="9">
+        <v>5</v>
+      </c>
+      <c r="H15" s="9">
+        <v>80</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>870</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+        <v>570</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="30">
+      <c r="A16" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="9">
+        <v>480</v>
+      </c>
+      <c r="C16" s="9">
+        <v>80</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>60</v>
+      </c>
+      <c r="F16" s="9">
+        <v>200</v>
+      </c>
+      <c r="G16" s="9">
+        <v>4</v>
+      </c>
+      <c r="H16" s="9">
+        <v>120</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="A17" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="9">
+        <v>620</v>
+      </c>
+      <c r="C17" s="9">
+        <v>50</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>200</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>870</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+        <v>570</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="30">
+      <c r="A18" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="9">
+        <v>600</v>
+      </c>
+      <c r="C18" s="9">
+        <v>100</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>300</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>440</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="8"/>
